--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1377"/>
+  <dimension ref="A1:B1378"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11379,6 +11379,14 @@
         <v>1.1625</v>
       </c>
     </row>
+    <row r="1378" spans="1:2">
+      <c r="A1378" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B1378">
+        <v>1.1602</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1378"/>
+  <dimension ref="A1:B1379"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11387,6 +11387,14 @@
         <v>1.1602</v>
       </c>
     </row>
+    <row r="1379" spans="1:2">
+      <c r="A1379" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B1379">
+        <v>1.1659</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1379"/>
+  <dimension ref="A1:B1380"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11395,6 +11395,14 @@
         <v>1.1659</v>
       </c>
     </row>
+    <row r="1380" spans="1:2">
+      <c r="A1380" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B1380">
+        <v>1.1519</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1380"/>
+  <dimension ref="A1:B1381"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11403,6 +11403,14 @@
         <v>1.1519</v>
       </c>
     </row>
+    <row r="1381" spans="1:2">
+      <c r="A1381" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B1381">
+        <v>1.1568</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1382"/>
+  <dimension ref="A1:B1383"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11445,6 +11445,14 @@
         <v>1.1468</v>
       </c>
     </row>
+    <row r="1383" spans="1:2">
+      <c r="A1383" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B1383">
+        <v>1.1383</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1383"/>
+  <dimension ref="A1:B1385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11453,6 +11453,22 @@
         <v>1.1383</v>
       </c>
     </row>
+    <row r="1384" spans="1:2">
+      <c r="A1384" s="3">
+        <v>46206</v>
+      </c>
+      <c r="B1384">
+        <v>1.1435</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:2">
+      <c r="A1385" s="3">
+        <v>46213</v>
+      </c>
+      <c r="B1385">
+        <v>1.1413</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1385"/>
+  <dimension ref="A1:B1386"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11469,6 +11469,14 @@
         <v>1.1413</v>
       </c>
     </row>
+    <row r="1386" spans="1:2">
+      <c r="A1386" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B1386">
+        <v>1.138205</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11474,7 +11474,7 @@
         <v>46220</v>
       </c>
       <c r="B1386">
-        <v>1.138205</v>
+        <v>1.14252</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11474,7 +11474,7 @@
         <v>46220</v>
       </c>
       <c r="B1386">
-        <v>1.14252</v>
+        <v>1.14685</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11474,7 +11474,7 @@
         <v>46220</v>
       </c>
       <c r="B1386">
-        <v>1.14685</v>
+        <v>1.144395</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11474,7 +11474,7 @@
         <v>46220</v>
       </c>
       <c r="B1386">
-        <v>1.144395</v>
+        <v>1.143045</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1386"/>
+  <dimension ref="A1:B1387"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11477,6 +11477,14 @@
         <v>1.143045</v>
       </c>
     </row>
+    <row r="1387" spans="1:2">
+      <c r="A1387" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B1387">
+        <v>1.141505</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11482,7 +11482,7 @@
         <v>46227</v>
       </c>
       <c r="B1387">
-        <v>1.141505</v>
+        <v>1.139965</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11482,7 +11482,7 @@
         <v>46227</v>
       </c>
       <c r="B1387">
-        <v>1.139965</v>
+        <v>1.14124</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11482,7 +11482,7 @@
         <v>46227</v>
       </c>
       <c r="B1387">
-        <v>1.14124</v>
+        <v>1.137675</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1387"/>
+  <dimension ref="A1:B1388"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11482,7 +11482,15 @@
         <v>46227</v>
       </c>
       <c r="B1387">
-        <v>1.137675</v>
+        <v>1.13931</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:2">
+      <c r="A1388" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B1388">
+        <v>1.137055</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11490,7 +11490,7 @@
         <v>46234</v>
       </c>
       <c r="B1388">
-        <v>1.137055</v>
+        <v>1.138385</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11490,7 +11490,7 @@
         <v>46234</v>
       </c>
       <c r="B1388">
-        <v>1.138385</v>
+        <v>1.145695</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11490,7 +11490,7 @@
         <v>46234</v>
       </c>
       <c r="B1388">
-        <v>1.145695</v>
+        <v>1.152235</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11490,7 +11490,7 @@
         <v>46234</v>
       </c>
       <c r="B1388">
-        <v>1.152235</v>
+        <v>1.154795</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1388"/>
+  <dimension ref="A1:B1389"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11493,6 +11493,14 @@
         <v>1.154795</v>
       </c>
     </row>
+    <row r="1389" spans="1:2">
+      <c r="A1389" s="3">
+        <v>46241</v>
+      </c>
+      <c r="B1389">
+        <v>1.15109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11498,7 +11498,7 @@
         <v>46241</v>
       </c>
       <c r="B1389">
-        <v>1.15109</v>
+        <v>1.15551</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11498,7 +11498,7 @@
         <v>46241</v>
       </c>
       <c r="B1389">
-        <v>1.15551</v>
+        <v>1.152205</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11498,7 +11498,7 @@
         <v>46241</v>
       </c>
       <c r="B1389">
-        <v>1.152205</v>
+        <v>1.156395</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1389"/>
+  <dimension ref="A1:B1390"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11501,6 +11501,14 @@
         <v>1.156395</v>
       </c>
     </row>
+    <row r="1390" spans="1:2">
+      <c r="A1390" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B1390">
+        <v>1.15413</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11506,7 +11506,7 @@
         <v>46248</v>
       </c>
       <c r="B1390">
-        <v>1.15413</v>
+        <v>1.153925</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11506,7 +11506,7 @@
         <v>46248</v>
       </c>
       <c r="B1390">
-        <v>1.153925</v>
+        <v>1.152885</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11506,7 +11506,7 @@
         <v>46248</v>
       </c>
       <c r="B1390">
-        <v>1.152885</v>
+        <v>1.15681</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11506,7 +11506,7 @@
         <v>46248</v>
       </c>
       <c r="B1390">
-        <v>1.15681</v>
+        <v>1.157015</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1390"/>
+  <dimension ref="A1:B1391"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11509,6 +11509,14 @@
         <v>1.157015</v>
       </c>
     </row>
+    <row r="1391" spans="1:2">
+      <c r="A1391" s="3">
+        <v>46255</v>
+      </c>
+      <c r="B1391">
+        <v>1.15778</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11514,7 +11514,7 @@
         <v>46255</v>
       </c>
       <c r="B1391">
-        <v>1.15778</v>
+        <v>1.160455</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11514,7 +11514,7 @@
         <v>46255</v>
       </c>
       <c r="B1391">
-        <v>1.160455</v>
+        <v>1.168215</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11514,7 +11514,7 @@
         <v>46255</v>
       </c>
       <c r="B1391">
-        <v>1.168215</v>
+        <v>1.17016</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11514,7 +11514,7 @@
         <v>46255</v>
       </c>
       <c r="B1391">
-        <v>1.17016</v>
+        <v>1.167495</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1391"/>
+  <dimension ref="A1:B1392"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11517,6 +11517,14 @@
         <v>1.167495</v>
       </c>
     </row>
+    <row r="1392" spans="1:2">
+      <c r="A1392" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B1392">
+        <v>1.16623</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11522,7 +11522,7 @@
         <v>46262</v>
       </c>
       <c r="B1392">
-        <v>1.16623</v>
+        <v>1.16689</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11522,7 +11522,7 @@
         <v>46262</v>
       </c>
       <c r="B1392">
-        <v>1.16689</v>
+        <v>1.164365</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11522,7 +11522,7 @@
         <v>46262</v>
       </c>
       <c r="B1392">
-        <v>1.164365</v>
+        <v>1.164555</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11522,7 +11522,7 @@
         <v>46262</v>
       </c>
       <c r="B1392">
-        <v>1.164555</v>
+        <v>1.1582</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1392"/>
+  <dimension ref="A1:B1393"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11525,6 +11525,14 @@
         <v>1.1582</v>
       </c>
     </row>
+    <row r="1393" spans="1:2">
+      <c r="A1393" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B1393">
+        <v>1.15919</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11530,7 +11530,7 @@
         <v>46269</v>
       </c>
       <c r="B1393">
-        <v>1.15919</v>
+        <v>1.15785</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11530,7 +11530,7 @@
         <v>46269</v>
       </c>
       <c r="B1393">
-        <v>1.15785</v>
+        <v>1.161295</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_diff_0th_diff.xlsx
+++ b/public/data/files/EURUSD_diff_0th_diff.xlsx
@@ -11530,7 +11530,7 @@
         <v>46269</v>
       </c>
       <c r="B1393">
-        <v>1.161295</v>
+        <v>1.162855</v>
       </c>
     </row>
   </sheetData>
